--- a/ppGpp_baza.xlsx
+++ b/ppGpp_baza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/944fa1a62d78ca82/Documents/Baza_ppGpp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2116" documentId="8_{4EEBD0DC-83F2-421B-A88E-9967EB44B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{661D8138-27C0-43D8-8C2A-701235EE935F}"/>
+  <xr:revisionPtr revIDLastSave="2118" documentId="8_{4EEBD0DC-83F2-421B-A88E-9967EB44B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9E8AE6F-85DC-4968-9114-D367473158D2}"/>
   <bookViews>
     <workbookView xWindow="6405" yWindow="1275" windowWidth="21165" windowHeight="13485" xr2:uid="{B489972C-9B8C-43F4-A381-2037D11F09BA}"/>
   </bookViews>
@@ -7000,7 +7000,7 @@
         <v>41</v>
       </c>
       <c r="D89" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="E89" t="s">
         <v>24</v>
@@ -7062,7 +7062,7 @@
         <v>41</v>
       </c>
       <c r="D90" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="E90" t="s">
         <v>24</v>
